--- a/Pricing Logic/modules/manual/output_702_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_702_chunk_1.xlsx
@@ -37,10 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>بريكس مزيل بقع - 30 جم</t>
-  </si>
-  <si>
-    <t>مولفيكس بانتس مقاس 4 - 56 حفاضة</t>
+    <t>لبن جهينة كامل الدسم - 1 لتر</t>
+  </si>
+  <si>
+    <t>ديرى  مثلثات - 8 قطعه</t>
   </si>
   <si>
     <t>YES</t>
@@ -429,7 +429,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>12503</v>
+        <v>248</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -438,7 +438,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>145</v>
+        <v>550</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -446,16 +446,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23234</v>
+        <v>21712</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>930</v>
+        <v>14.25</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -463,16 +463,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23234</v>
+        <v>21712</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>310</v>
+        <v>513</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>

--- a/Pricing Logic/modules/manual/output_702_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_702_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>لبن جهينة كامل الدسم - 1 لتر</t>
-  </si>
-  <si>
-    <t>ديرى  مثلثات - 8 قطعه</t>
+    <t>ستينج فراولة زجاج - 275 مل</t>
+  </si>
+  <si>
+    <t>مناديل بابيا جيب كلاسيك 3 طبقة - 10 باكت</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,16 +429,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>248</v>
+        <v>1124</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>550</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -446,35 +446,18 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21712</v>
+        <v>5976</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>14.25</v>
+        <v>182.25</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21712</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>513</v>
-      </c>
-      <c r="E4" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Pricing Logic/modules/manual/output_702_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_702_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>ستينج فراولة زجاج - 275 مل</t>
-  </si>
-  <si>
-    <t>مناديل بابيا جيب كلاسيك 3 طبقة - 10 باكت</t>
+    <t>صابون لوكس بشرة مثالية - 75 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس بشرة نضرة - 75 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,7 +429,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>1124</v>
+        <v>11435</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -438,7 +438,7 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>158</v>
+        <v>60.5</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -446,18 +446,52 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>5976</v>
+        <v>11435</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>182.25</v>
+        <v>484</v>
       </c>
       <c r="E3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>11450</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>59.5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>11450</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>476</v>
+      </c>
+      <c r="E5" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Pricing Logic/modules/manual/output_702_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_702_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,61 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>نوفي فينجرز شيكولاتة بيضاء - 5 جنية</t>
+    <t>زيت كريستال الممتاز خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال الممتاز خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت قلية خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت قلية خليط - 2.1 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت صنى خليط عباد الشمس - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت صنى خليط عباد الشمس - 2.4 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 6 زجاجة - 1.6 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 900 مل</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 6 زجاجة - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1.8 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال الممتاز خليط - 2.5 لتر</t>
+  </si>
+  <si>
+    <t>زيت قلية خليط - 4.5 لتر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 550 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,7 +480,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21687</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,27 +489,316 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>327</v>
+        <v>866</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21687</v>
+        <v>448</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>27.25</v>
+        <v>625</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>470</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>863.5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>471</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>612.25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>1492</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>860</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>2161</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>656</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>2608</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>725.25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>2879</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>810</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>2934</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1066</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>2935</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>892.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>6496</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>758</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>6497</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>855</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>7324</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>480.5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>9358</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>554</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>11961</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>533.25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>11965</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>705.25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>11968</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1262</v>
+      </c>
+      <c r="E18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>12923</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>855</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>12925</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>490</v>
+      </c>
+      <c r="E20" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/manual/output_702_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_702_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>دومتي عصير مانجو- 1 لتر</t>
-  </si>
-  <si>
-    <t>توشيبا احمر ريموت كارت AAA - 4 حجر</t>
+    <t>كوكا كولا زيرو - 320 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>3865</v>
+        <v>4246</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -438,44 +435,10 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>290</v>
+        <v>339</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>12608</v>
-      </c>
-      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>370</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>12608</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1850</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
